--- a/grupos/6ALCM - Estadisticos 20212.xlsx
+++ b/grupos/6ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="152">
   <si>
     <t>Materia</t>
   </si>
@@ -188,19 +188,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
+    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
@@ -962,19 +962,19 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>-1</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1016,19 +1016,19 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1039,19 +1039,19 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D5">
         <v>-1</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1093,19 +1093,19 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1125,10 +1125,10 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1170,7 +1170,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1179,10 +1179,10 @@
         <v>-1</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1193,19 +1193,19 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>-1</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1247,19 +1247,19 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1270,19 +1270,19 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>-1</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1324,19 +1324,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1347,19 +1347,19 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1401,19 +1401,19 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1424,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1433,10 +1433,10 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1478,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1487,10 +1487,10 @@
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1501,7 +1501,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1510,10 +1510,10 @@
         <v>-1</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1555,7 +1555,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1564,10 +1564,10 @@
         <v>-1</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1578,19 +1578,19 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1632,19 +1632,19 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1655,19 +1655,19 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1709,19 +1709,19 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1744,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1798,7 +1798,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1809,7 +1809,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1818,10 +1818,10 @@
         <v>-1</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1872,10 +1872,10 @@
         <v>-1</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1886,19 +1886,19 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1940,19 +1940,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1963,7 +1963,7 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -1972,10 +1972,10 @@
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2017,7 +2017,7 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2026,10 +2026,10 @@
         <v>-1</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2040,19 +2040,19 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2094,19 +2094,19 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2117,19 +2117,19 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>-1</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2171,19 +2171,19 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2194,19 +2194,19 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F20">
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2248,19 +2248,19 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>-1</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2271,7 +2271,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2280,10 +2280,10 @@
         <v>-1</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2325,7 +2325,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2334,10 +2334,10 @@
         <v>-1</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2348,19 +2348,19 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>-1</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2402,19 +2402,19 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2425,19 +2425,19 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2479,19 +2479,19 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2502,19 +2502,19 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D24">
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2556,19 +2556,19 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2588,10 +2588,10 @@
         <v>-1</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2642,10 +2642,10 @@
         <v>-1</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2656,19 +2656,19 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2710,19 +2710,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2733,19 +2733,19 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D27">
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2787,19 +2787,19 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2810,19 +2810,19 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>-1</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2864,19 +2864,19 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2887,19 +2887,19 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2941,19 +2941,19 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2964,19 +2964,19 @@
         <v>10</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D30">
         <v>-1</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3018,19 +3018,19 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3041,19 +3041,19 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3095,19 +3095,19 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3118,7 +3118,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3127,10 +3127,10 @@
         <v>-1</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3172,7 +3172,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3181,10 +3181,10 @@
         <v>-1</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3195,19 +3195,19 @@
         <v>10</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>-1</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3249,19 +3249,19 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3272,19 +3272,19 @@
         <v>7</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>-1</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3326,19 +3326,19 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3349,19 +3349,19 @@
         <v>8</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3403,19 +3403,19 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3426,7 +3426,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>-1</v>
@@ -3435,10 +3435,10 @@
         <v>-1</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3480,7 +3480,7 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>-1</v>
@@ -3489,10 +3489,10 @@
         <v>-1</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3503,19 +3503,19 @@
         <v>10</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3557,19 +3557,19 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3580,19 +3580,19 @@
         <v>8</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>-1</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3634,19 +3634,19 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3740,27 +3740,30 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7.9</v>
+      </c>
       <c r="I3">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3769,27 +3772,30 @@
         <v>35</v>
       </c>
       <c r="D4">
+        <v>27</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>77.14</v>
+      </c>
+      <c r="G4">
+        <v>22.86</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>35</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3798,27 +3804,30 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>8.57</v>
+      </c>
+      <c r="H5">
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -3827,22 +3836,25 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
+      <c r="H6">
+        <v>9.5</v>
+      </c>
       <c r="I6">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3884,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3925,7 +3937,7 @@
         <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -3933,99 +3945,99 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920148</v>
+        <v>19330051920149</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920148</v>
+        <v>19330051920150</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920148</v>
+        <v>19330051920150</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920148</v>
+        <v>19330051920153</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920149</v>
+        <v>19330051920152</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>56</v>
@@ -4033,99 +4045,99 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920149</v>
+        <v>19330051920154</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920149</v>
+        <v>19330051920154</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920149</v>
+        <v>19330051920276</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920149</v>
+        <v>19330051920276</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920150</v>
+        <v>19330051920151</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
@@ -4133,99 +4145,99 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920150</v>
+        <v>19330051920157</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920150</v>
+        <v>19330051920157</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920150</v>
+        <v>19330051920157</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920150</v>
+        <v>19330051920157</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920153</v>
+        <v>19330051920160</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>56</v>
@@ -4233,99 +4245,99 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920153</v>
+        <v>19330051920158</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920153</v>
+        <v>19330051920158</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920153</v>
+        <v>19330051920159</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920153</v>
+        <v>19330051920159</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920152</v>
+        <v>19330051920423</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
         <v>56</v>
@@ -4333,199 +4345,199 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920152</v>
+        <v>19330051920281</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920152</v>
+        <v>19330051920161</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920152</v>
+        <v>19330051920161</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920152</v>
+        <v>19330051920162</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920154</v>
+        <v>19330051920162</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920154</v>
+        <v>19330051920155</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920154</v>
+        <v>19330051920163</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920154</v>
+        <v>19330051920156</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920154</v>
+        <v>19330051920165</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920276</v>
+        <v>19330051920166</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
         <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
         <v>56</v>
@@ -4533,99 +4545,99 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920276</v>
+        <v>19330051920168</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920276</v>
+        <v>19330051920168</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920276</v>
+        <v>19330051920170</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920276</v>
+        <v>19330051920172</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920151</v>
+        <v>19330051920173</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
         <v>56</v>
@@ -4633,2782 +4645,242 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920151</v>
+        <v>19330051920176</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920151</v>
+        <v>19330051920174</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>19330051920151</v>
+        <v>19330051920175</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C40" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>19330051920151</v>
+        <v>19330051920178</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920157</v>
+        <v>19330051920178</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>19330051920157</v>
+        <v>19330051920179</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920157</v>
+        <v>19330051920181</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>19330051920157</v>
+        <v>19330051920180</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>19330051920157</v>
+        <v>19330051920303</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>19330051920160</v>
+        <v>19330051920303</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>19330051920160</v>
+        <v>19330051920182</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>19330051920160</v>
+        <v>19330051920183</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920160</v>
-      </c>
-      <c r="B50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920160</v>
-      </c>
-      <c r="B51" t="s">
-        <v>75</v>
-      </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" t="s">
-        <v>127</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920158</v>
-      </c>
-      <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
-        <v>102</v>
-      </c>
-      <c r="D52" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920158</v>
-      </c>
-      <c r="B53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" t="s">
-        <v>128</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920158</v>
-      </c>
-      <c r="B54" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" t="s">
-        <v>128</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920158</v>
-      </c>
-      <c r="B55" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920158</v>
-      </c>
-      <c r="B56" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" t="s">
-        <v>102</v>
-      </c>
-      <c r="D56" t="s">
-        <v>128</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920159</v>
-      </c>
-      <c r="B57" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" t="s">
-        <v>93</v>
-      </c>
-      <c r="D57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920159</v>
-      </c>
-      <c r="B58" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" t="s">
-        <v>93</v>
-      </c>
-      <c r="D58" t="s">
-        <v>129</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920159</v>
-      </c>
-      <c r="B59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>93</v>
-      </c>
-      <c r="D59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920159</v>
-      </c>
-      <c r="B60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" t="s">
-        <v>93</v>
-      </c>
-      <c r="D60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920159</v>
-      </c>
-      <c r="B61" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" t="s">
-        <v>129</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920423</v>
-      </c>
-      <c r="B62" t="s">
-        <v>77</v>
-      </c>
-      <c r="C62" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" t="s">
-        <v>130</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920423</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C63" t="s">
-        <v>103</v>
-      </c>
-      <c r="D63" t="s">
-        <v>130</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920423</v>
-      </c>
-      <c r="B64" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" t="s">
-        <v>103</v>
-      </c>
-      <c r="D64" t="s">
-        <v>130</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920423</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" t="s">
-        <v>103</v>
-      </c>
-      <c r="D65" t="s">
-        <v>130</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920423</v>
-      </c>
-      <c r="B66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" t="s">
-        <v>130</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920281</v>
-      </c>
-      <c r="B67" t="s">
-        <v>77</v>
-      </c>
-      <c r="C67" t="s">
-        <v>78</v>
-      </c>
-      <c r="D67" t="s">
-        <v>131</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920281</v>
-      </c>
-      <c r="B68" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68" t="s">
-        <v>78</v>
-      </c>
-      <c r="D68" t="s">
-        <v>131</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920281</v>
-      </c>
-      <c r="B69" t="s">
-        <v>77</v>
-      </c>
-      <c r="C69" t="s">
-        <v>78</v>
-      </c>
-      <c r="D69" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920281</v>
-      </c>
-      <c r="B70" t="s">
-        <v>77</v>
-      </c>
-      <c r="C70" t="s">
-        <v>78</v>
-      </c>
-      <c r="D70" t="s">
-        <v>131</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920281</v>
-      </c>
-      <c r="B71" t="s">
-        <v>77</v>
-      </c>
-      <c r="C71" t="s">
-        <v>78</v>
-      </c>
-      <c r="D71" t="s">
-        <v>131</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920161</v>
-      </c>
-      <c r="B72" t="s">
-        <v>78</v>
-      </c>
-      <c r="C72" t="s">
-        <v>104</v>
-      </c>
-      <c r="D72" t="s">
-        <v>132</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920161</v>
-      </c>
-      <c r="B73" t="s">
-        <v>78</v>
-      </c>
-      <c r="C73" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" t="s">
-        <v>132</v>
-      </c>
-      <c r="E73" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920161</v>
-      </c>
-      <c r="B74" t="s">
-        <v>78</v>
-      </c>
-      <c r="C74" t="s">
-        <v>104</v>
-      </c>
-      <c r="D74" t="s">
-        <v>132</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920161</v>
-      </c>
-      <c r="B75" t="s">
-        <v>78</v>
-      </c>
-      <c r="C75" t="s">
-        <v>104</v>
-      </c>
-      <c r="D75" t="s">
-        <v>132</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920161</v>
-      </c>
-      <c r="B76" t="s">
-        <v>78</v>
-      </c>
-      <c r="C76" t="s">
-        <v>104</v>
-      </c>
-      <c r="D76" t="s">
-        <v>132</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920162</v>
-      </c>
-      <c r="B77" t="s">
-        <v>79</v>
-      </c>
-      <c r="C77" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" t="s">
-        <v>133</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920162</v>
-      </c>
-      <c r="B78" t="s">
-        <v>79</v>
-      </c>
-      <c r="C78" t="s">
-        <v>105</v>
-      </c>
-      <c r="D78" t="s">
-        <v>133</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920162</v>
-      </c>
-      <c r="B79" t="s">
-        <v>79</v>
-      </c>
-      <c r="C79" t="s">
-        <v>105</v>
-      </c>
-      <c r="D79" t="s">
-        <v>133</v>
-      </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920162</v>
-      </c>
-      <c r="B80" t="s">
-        <v>79</v>
-      </c>
-      <c r="C80" t="s">
-        <v>105</v>
-      </c>
-      <c r="D80" t="s">
-        <v>133</v>
-      </c>
-      <c r="E80" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920162</v>
-      </c>
-      <c r="B81" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" t="s">
-        <v>105</v>
-      </c>
-      <c r="D81" t="s">
-        <v>133</v>
-      </c>
-      <c r="E81" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920155</v>
-      </c>
-      <c r="B82" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" t="s">
-        <v>106</v>
-      </c>
-      <c r="D82" t="s">
-        <v>134</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>19330051920155</v>
-      </c>
-      <c r="B83" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" t="s">
-        <v>106</v>
-      </c>
-      <c r="D83" t="s">
-        <v>134</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>19330051920155</v>
-      </c>
-      <c r="B84" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" t="s">
-        <v>106</v>
-      </c>
-      <c r="D84" t="s">
-        <v>134</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>19330051920155</v>
-      </c>
-      <c r="B85" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" t="s">
-        <v>106</v>
-      </c>
-      <c r="D85" t="s">
-        <v>134</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>19330051920155</v>
-      </c>
-      <c r="B86" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" t="s">
-        <v>106</v>
-      </c>
-      <c r="D86" t="s">
-        <v>134</v>
-      </c>
-      <c r="E86" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>19330051920163</v>
-      </c>
-      <c r="B87" t="s">
-        <v>81</v>
-      </c>
-      <c r="C87" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" t="s">
-        <v>135</v>
-      </c>
-      <c r="E87" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>19330051920163</v>
-      </c>
-      <c r="B88" t="s">
-        <v>81</v>
-      </c>
-      <c r="C88" t="s">
-        <v>89</v>
-      </c>
-      <c r="D88" t="s">
-        <v>135</v>
-      </c>
-      <c r="E88" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920163</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89" t="s">
-        <v>89</v>
-      </c>
-      <c r="D89" t="s">
-        <v>135</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920163</v>
-      </c>
-      <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" t="s">
-        <v>89</v>
-      </c>
-      <c r="D90" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920163</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" t="s">
-        <v>89</v>
-      </c>
-      <c r="D91" t="s">
-        <v>135</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920156</v>
-      </c>
-      <c r="B92" t="s">
-        <v>82</v>
-      </c>
-      <c r="C92" t="s">
-        <v>89</v>
-      </c>
-      <c r="D92" t="s">
-        <v>136</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920156</v>
-      </c>
-      <c r="B93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C93" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" t="s">
-        <v>136</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920156</v>
-      </c>
-      <c r="B94" t="s">
-        <v>82</v>
-      </c>
-      <c r="C94" t="s">
-        <v>89</v>
-      </c>
-      <c r="D94" t="s">
-        <v>136</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920156</v>
-      </c>
-      <c r="B95" t="s">
-        <v>82</v>
-      </c>
-      <c r="C95" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" t="s">
-        <v>136</v>
-      </c>
-      <c r="E95" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920156</v>
-      </c>
-      <c r="B96" t="s">
-        <v>82</v>
-      </c>
-      <c r="C96" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" t="s">
-        <v>136</v>
-      </c>
-      <c r="E96" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920165</v>
-      </c>
-      <c r="B97" t="s">
-        <v>83</v>
-      </c>
-      <c r="C97" t="s">
-        <v>107</v>
-      </c>
-      <c r="D97" t="s">
-        <v>137</v>
-      </c>
-      <c r="E97" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920165</v>
-      </c>
-      <c r="B98" t="s">
-        <v>83</v>
-      </c>
-      <c r="C98" t="s">
-        <v>107</v>
-      </c>
-      <c r="D98" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920165</v>
-      </c>
-      <c r="B99" t="s">
-        <v>83</v>
-      </c>
-      <c r="C99" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" t="s">
-        <v>137</v>
-      </c>
-      <c r="E99" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>19330051920165</v>
-      </c>
-      <c r="B100" t="s">
-        <v>83</v>
-      </c>
-      <c r="C100" t="s">
-        <v>107</v>
-      </c>
-      <c r="D100" t="s">
-        <v>137</v>
-      </c>
-      <c r="E100" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>19330051920165</v>
-      </c>
-      <c r="B101" t="s">
-        <v>83</v>
-      </c>
-      <c r="C101" t="s">
-        <v>107</v>
-      </c>
-      <c r="D101" t="s">
-        <v>137</v>
-      </c>
-      <c r="E101" t="s">
-        <v>6</v>
-      </c>
-      <c r="F101" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>19330051920166</v>
-      </c>
-      <c r="B102" t="s">
-        <v>84</v>
-      </c>
-      <c r="C102" t="s">
-        <v>108</v>
-      </c>
-      <c r="D102" t="s">
-        <v>124</v>
-      </c>
-      <c r="E102" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>19330051920166</v>
-      </c>
-      <c r="B103" t="s">
-        <v>84</v>
-      </c>
-      <c r="C103" t="s">
-        <v>108</v>
-      </c>
-      <c r="D103" t="s">
-        <v>124</v>
-      </c>
-      <c r="E103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>19330051920166</v>
-      </c>
-      <c r="B104" t="s">
-        <v>84</v>
-      </c>
-      <c r="C104" t="s">
-        <v>108</v>
-      </c>
-      <c r="D104" t="s">
-        <v>124</v>
-      </c>
-      <c r="E104" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>19330051920166</v>
-      </c>
-      <c r="B105" t="s">
-        <v>84</v>
-      </c>
-      <c r="C105" t="s">
-        <v>108</v>
-      </c>
-      <c r="D105" t="s">
-        <v>124</v>
-      </c>
-      <c r="E105" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>19330051920166</v>
-      </c>
-      <c r="B106" t="s">
-        <v>84</v>
-      </c>
-      <c r="C106" t="s">
-        <v>108</v>
-      </c>
-      <c r="D106" t="s">
-        <v>124</v>
-      </c>
-      <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>19330051920168</v>
-      </c>
-      <c r="B107" t="s">
-        <v>85</v>
-      </c>
-      <c r="C107" t="s">
-        <v>80</v>
-      </c>
-      <c r="D107" t="s">
-        <v>138</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>19330051920168</v>
-      </c>
-      <c r="B108" t="s">
-        <v>85</v>
-      </c>
-      <c r="C108" t="s">
-        <v>80</v>
-      </c>
-      <c r="D108" t="s">
-        <v>138</v>
-      </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>19330051920168</v>
-      </c>
-      <c r="B109" t="s">
-        <v>85</v>
-      </c>
-      <c r="C109" t="s">
-        <v>80</v>
-      </c>
-      <c r="D109" t="s">
-        <v>138</v>
-      </c>
-      <c r="E109" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>19330051920168</v>
-      </c>
-      <c r="B110" t="s">
-        <v>85</v>
-      </c>
-      <c r="C110" t="s">
-        <v>80</v>
-      </c>
-      <c r="D110" t="s">
-        <v>138</v>
-      </c>
-      <c r="E110" t="s">
-        <v>8</v>
-      </c>
-      <c r="F110" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>19330051920168</v>
-      </c>
-      <c r="B111" t="s">
-        <v>85</v>
-      </c>
-      <c r="C111" t="s">
-        <v>80</v>
-      </c>
-      <c r="D111" t="s">
-        <v>138</v>
-      </c>
-      <c r="E111" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>19330051920170</v>
-      </c>
-      <c r="B112" t="s">
-        <v>86</v>
-      </c>
-      <c r="C112" t="s">
-        <v>78</v>
-      </c>
-      <c r="D112" t="s">
-        <v>139</v>
-      </c>
-      <c r="E112" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>19330051920170</v>
-      </c>
-      <c r="B113" t="s">
-        <v>86</v>
-      </c>
-      <c r="C113" t="s">
-        <v>78</v>
-      </c>
-      <c r="D113" t="s">
-        <v>139</v>
-      </c>
-      <c r="E113" t="s">
-        <v>7</v>
-      </c>
-      <c r="F113" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>19330051920170</v>
-      </c>
-      <c r="B114" t="s">
-        <v>86</v>
-      </c>
-      <c r="C114" t="s">
-        <v>78</v>
-      </c>
-      <c r="D114" t="s">
-        <v>139</v>
-      </c>
-      <c r="E114" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>19330051920170</v>
-      </c>
-      <c r="B115" t="s">
-        <v>86</v>
-      </c>
-      <c r="C115" t="s">
-        <v>78</v>
-      </c>
-      <c r="D115" t="s">
-        <v>139</v>
-      </c>
-      <c r="E115" t="s">
-        <v>8</v>
-      </c>
-      <c r="F115" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>19330051920170</v>
-      </c>
-      <c r="B116" t="s">
-        <v>86</v>
-      </c>
-      <c r="C116" t="s">
-        <v>78</v>
-      </c>
-      <c r="D116" t="s">
-        <v>139</v>
-      </c>
-      <c r="E116" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>19330051920172</v>
-      </c>
-      <c r="B117" t="s">
-        <v>87</v>
-      </c>
-      <c r="C117" t="s">
-        <v>94</v>
-      </c>
-      <c r="D117" t="s">
-        <v>140</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>19330051920172</v>
-      </c>
-      <c r="B118" t="s">
-        <v>87</v>
-      </c>
-      <c r="C118" t="s">
-        <v>94</v>
-      </c>
-      <c r="D118" t="s">
-        <v>140</v>
-      </c>
-      <c r="E118" t="s">
-        <v>7</v>
-      </c>
-      <c r="F118" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>19330051920172</v>
-      </c>
-      <c r="B119" t="s">
-        <v>87</v>
-      </c>
-      <c r="C119" t="s">
-        <v>94</v>
-      </c>
-      <c r="D119" t="s">
-        <v>140</v>
-      </c>
-      <c r="E119" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>19330051920172</v>
-      </c>
-      <c r="B120" t="s">
-        <v>87</v>
-      </c>
-      <c r="C120" t="s">
-        <v>94</v>
-      </c>
-      <c r="D120" t="s">
-        <v>140</v>
-      </c>
-      <c r="E120" t="s">
-        <v>8</v>
-      </c>
-      <c r="F120" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>19330051920172</v>
-      </c>
-      <c r="B121" t="s">
-        <v>87</v>
-      </c>
-      <c r="C121" t="s">
-        <v>94</v>
-      </c>
-      <c r="D121" t="s">
-        <v>140</v>
-      </c>
-      <c r="E121" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>19330051920173</v>
-      </c>
-      <c r="B122" t="s">
-        <v>88</v>
-      </c>
-      <c r="C122" t="s">
-        <v>109</v>
-      </c>
-      <c r="D122" t="s">
-        <v>141</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>19330051920173</v>
-      </c>
-      <c r="B123" t="s">
-        <v>88</v>
-      </c>
-      <c r="C123" t="s">
-        <v>109</v>
-      </c>
-      <c r="D123" t="s">
-        <v>141</v>
-      </c>
-      <c r="E123" t="s">
-        <v>7</v>
-      </c>
-      <c r="F123" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>19330051920173</v>
-      </c>
-      <c r="B124" t="s">
-        <v>88</v>
-      </c>
-      <c r="C124" t="s">
-        <v>109</v>
-      </c>
-      <c r="D124" t="s">
-        <v>141</v>
-      </c>
-      <c r="E124" t="s">
-        <v>9</v>
-      </c>
-      <c r="F124" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>19330051920173</v>
-      </c>
-      <c r="B125" t="s">
-        <v>88</v>
-      </c>
-      <c r="C125" t="s">
-        <v>109</v>
-      </c>
-      <c r="D125" t="s">
-        <v>141</v>
-      </c>
-      <c r="E125" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>19330051920173</v>
-      </c>
-      <c r="B126" t="s">
-        <v>88</v>
-      </c>
-      <c r="C126" t="s">
-        <v>109</v>
-      </c>
-      <c r="D126" t="s">
-        <v>141</v>
-      </c>
-      <c r="E126" t="s">
-        <v>6</v>
-      </c>
-      <c r="F126" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>19330051920176</v>
-      </c>
-      <c r="B127" t="s">
-        <v>89</v>
-      </c>
-      <c r="C127" t="s">
-        <v>110</v>
-      </c>
-      <c r="D127" t="s">
-        <v>142</v>
-      </c>
-      <c r="E127" t="s">
-        <v>10</v>
-      </c>
-      <c r="F127" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>19330051920176</v>
-      </c>
-      <c r="B128" t="s">
-        <v>89</v>
-      </c>
-      <c r="C128" t="s">
-        <v>110</v>
-      </c>
-      <c r="D128" t="s">
-        <v>142</v>
-      </c>
-      <c r="E128" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>19330051920176</v>
-      </c>
-      <c r="B129" t="s">
-        <v>89</v>
-      </c>
-      <c r="C129" t="s">
-        <v>110</v>
-      </c>
-      <c r="D129" t="s">
-        <v>142</v>
-      </c>
-      <c r="E129" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>19330051920176</v>
-      </c>
-      <c r="B130" t="s">
-        <v>89</v>
-      </c>
-      <c r="C130" t="s">
-        <v>110</v>
-      </c>
-      <c r="D130" t="s">
-        <v>142</v>
-      </c>
-      <c r="E130" t="s">
-        <v>8</v>
-      </c>
-      <c r="F130" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>19330051920176</v>
-      </c>
-      <c r="B131" t="s">
-        <v>89</v>
-      </c>
-      <c r="C131" t="s">
-        <v>110</v>
-      </c>
-      <c r="D131" t="s">
-        <v>142</v>
-      </c>
-      <c r="E131" t="s">
-        <v>6</v>
-      </c>
-      <c r="F131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>19330051920174</v>
-      </c>
-      <c r="B132" t="s">
-        <v>89</v>
-      </c>
-      <c r="C132" t="s">
-        <v>111</v>
-      </c>
-      <c r="D132" t="s">
-        <v>143</v>
-      </c>
-      <c r="E132" t="s">
-        <v>10</v>
-      </c>
-      <c r="F132" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>19330051920174</v>
-      </c>
-      <c r="B133" t="s">
-        <v>89</v>
-      </c>
-      <c r="C133" t="s">
-        <v>111</v>
-      </c>
-      <c r="D133" t="s">
-        <v>143</v>
-      </c>
-      <c r="E133" t="s">
-        <v>7</v>
-      </c>
-      <c r="F133" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>19330051920174</v>
-      </c>
-      <c r="B134" t="s">
-        <v>89</v>
-      </c>
-      <c r="C134" t="s">
-        <v>111</v>
-      </c>
-      <c r="D134" t="s">
-        <v>143</v>
-      </c>
-      <c r="E134" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>19330051920174</v>
-      </c>
-      <c r="B135" t="s">
-        <v>89</v>
-      </c>
-      <c r="C135" t="s">
-        <v>111</v>
-      </c>
-      <c r="D135" t="s">
-        <v>143</v>
-      </c>
-      <c r="E135" t="s">
-        <v>8</v>
-      </c>
-      <c r="F135" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>19330051920174</v>
-      </c>
-      <c r="B136" t="s">
-        <v>89</v>
-      </c>
-      <c r="C136" t="s">
-        <v>111</v>
-      </c>
-      <c r="D136" t="s">
-        <v>143</v>
-      </c>
-      <c r="E136" t="s">
-        <v>6</v>
-      </c>
-      <c r="F136" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>19330051920175</v>
-      </c>
-      <c r="B137" t="s">
-        <v>89</v>
-      </c>
-      <c r="C137" t="s">
-        <v>92</v>
-      </c>
-      <c r="D137" t="s">
-        <v>144</v>
-      </c>
-      <c r="E137" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>19330051920175</v>
-      </c>
-      <c r="B138" t="s">
-        <v>89</v>
-      </c>
-      <c r="C138" t="s">
-        <v>92</v>
-      </c>
-      <c r="D138" t="s">
-        <v>144</v>
-      </c>
-      <c r="E138" t="s">
-        <v>7</v>
-      </c>
-      <c r="F138" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>19330051920175</v>
-      </c>
-      <c r="B139" t="s">
-        <v>89</v>
-      </c>
-      <c r="C139" t="s">
-        <v>92</v>
-      </c>
-      <c r="D139" t="s">
-        <v>144</v>
-      </c>
-      <c r="E139" t="s">
-        <v>9</v>
-      </c>
-      <c r="F139" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>19330051920175</v>
-      </c>
-      <c r="B140" t="s">
-        <v>89</v>
-      </c>
-      <c r="C140" t="s">
-        <v>92</v>
-      </c>
-      <c r="D140" t="s">
-        <v>144</v>
-      </c>
-      <c r="E140" t="s">
-        <v>8</v>
-      </c>
-      <c r="F140" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>19330051920175</v>
-      </c>
-      <c r="B141" t="s">
-        <v>89</v>
-      </c>
-      <c r="C141" t="s">
-        <v>92</v>
-      </c>
-      <c r="D141" t="s">
-        <v>144</v>
-      </c>
-      <c r="E141" t="s">
-        <v>6</v>
-      </c>
-      <c r="F141" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>19330051920178</v>
-      </c>
-      <c r="B142" t="s">
-        <v>90</v>
-      </c>
-      <c r="C142" t="s">
-        <v>112</v>
-      </c>
-      <c r="D142" t="s">
-        <v>145</v>
-      </c>
-      <c r="E142" t="s">
-        <v>10</v>
-      </c>
-      <c r="F142" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>19330051920178</v>
-      </c>
-      <c r="B143" t="s">
-        <v>90</v>
-      </c>
-      <c r="C143" t="s">
-        <v>112</v>
-      </c>
-      <c r="D143" t="s">
-        <v>145</v>
-      </c>
-      <c r="E143" t="s">
-        <v>7</v>
-      </c>
-      <c r="F143" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>19330051920178</v>
-      </c>
-      <c r="B144" t="s">
-        <v>90</v>
-      </c>
-      <c r="C144" t="s">
-        <v>112</v>
-      </c>
-      <c r="D144" t="s">
-        <v>145</v>
-      </c>
-      <c r="E144" t="s">
-        <v>9</v>
-      </c>
-      <c r="F144" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>19330051920178</v>
-      </c>
-      <c r="B145" t="s">
-        <v>90</v>
-      </c>
-      <c r="C145" t="s">
-        <v>112</v>
-      </c>
-      <c r="D145" t="s">
-        <v>145</v>
-      </c>
-      <c r="E145" t="s">
-        <v>8</v>
-      </c>
-      <c r="F145" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>19330051920178</v>
-      </c>
-      <c r="B146" t="s">
-        <v>90</v>
-      </c>
-      <c r="C146" t="s">
-        <v>112</v>
-      </c>
-      <c r="D146" t="s">
-        <v>145</v>
-      </c>
-      <c r="E146" t="s">
-        <v>6</v>
-      </c>
-      <c r="F146" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>19330051920179</v>
-      </c>
-      <c r="B147" t="s">
-        <v>91</v>
-      </c>
-      <c r="C147" t="s">
-        <v>75</v>
-      </c>
-      <c r="D147" t="s">
-        <v>146</v>
-      </c>
-      <c r="E147" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>19330051920179</v>
-      </c>
-      <c r="B148" t="s">
-        <v>91</v>
-      </c>
-      <c r="C148" t="s">
-        <v>75</v>
-      </c>
-      <c r="D148" t="s">
-        <v>146</v>
-      </c>
-      <c r="E148" t="s">
-        <v>7</v>
-      </c>
-      <c r="F148" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>19330051920179</v>
-      </c>
-      <c r="B149" t="s">
-        <v>91</v>
-      </c>
-      <c r="C149" t="s">
-        <v>75</v>
-      </c>
-      <c r="D149" t="s">
-        <v>146</v>
-      </c>
-      <c r="E149" t="s">
-        <v>9</v>
-      </c>
-      <c r="F149" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>19330051920179</v>
-      </c>
-      <c r="B150" t="s">
-        <v>91</v>
-      </c>
-      <c r="C150" t="s">
-        <v>75</v>
-      </c>
-      <c r="D150" t="s">
-        <v>146</v>
-      </c>
-      <c r="E150" t="s">
-        <v>8</v>
-      </c>
-      <c r="F150" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>19330051920179</v>
-      </c>
-      <c r="B151" t="s">
-        <v>91</v>
-      </c>
-      <c r="C151" t="s">
-        <v>75</v>
-      </c>
-      <c r="D151" t="s">
-        <v>146</v>
-      </c>
-      <c r="E151" t="s">
-        <v>6</v>
-      </c>
-      <c r="F151" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>19330051920181</v>
-      </c>
-      <c r="B152" t="s">
-        <v>91</v>
-      </c>
-      <c r="C152" t="s">
-        <v>113</v>
-      </c>
-      <c r="D152" t="s">
-        <v>147</v>
-      </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>19330051920181</v>
-      </c>
-      <c r="B153" t="s">
-        <v>91</v>
-      </c>
-      <c r="C153" t="s">
-        <v>113</v>
-      </c>
-      <c r="D153" t="s">
-        <v>147</v>
-      </c>
-      <c r="E153" t="s">
-        <v>7</v>
-      </c>
-      <c r="F153" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>19330051920181</v>
-      </c>
-      <c r="B154" t="s">
-        <v>91</v>
-      </c>
-      <c r="C154" t="s">
-        <v>113</v>
-      </c>
-      <c r="D154" t="s">
-        <v>147</v>
-      </c>
-      <c r="E154" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>19330051920181</v>
-      </c>
-      <c r="B155" t="s">
-        <v>91</v>
-      </c>
-      <c r="C155" t="s">
-        <v>113</v>
-      </c>
-      <c r="D155" t="s">
-        <v>147</v>
-      </c>
-      <c r="E155" t="s">
-        <v>8</v>
-      </c>
-      <c r="F155" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>19330051920181</v>
-      </c>
-      <c r="B156" t="s">
-        <v>91</v>
-      </c>
-      <c r="C156" t="s">
-        <v>113</v>
-      </c>
-      <c r="D156" t="s">
-        <v>147</v>
-      </c>
-      <c r="E156" t="s">
-        <v>6</v>
-      </c>
-      <c r="F156" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>19330051920180</v>
-      </c>
-      <c r="B157" t="s">
-        <v>91</v>
-      </c>
-      <c r="C157" t="s">
-        <v>114</v>
-      </c>
-      <c r="D157" t="s">
-        <v>148</v>
-      </c>
-      <c r="E157" t="s">
-        <v>10</v>
-      </c>
-      <c r="F157" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>19330051920180</v>
-      </c>
-      <c r="B158" t="s">
-        <v>91</v>
-      </c>
-      <c r="C158" t="s">
-        <v>114</v>
-      </c>
-      <c r="D158" t="s">
-        <v>148</v>
-      </c>
-      <c r="E158" t="s">
-        <v>7</v>
-      </c>
-      <c r="F158" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>19330051920180</v>
-      </c>
-      <c r="B159" t="s">
-        <v>91</v>
-      </c>
-      <c r="C159" t="s">
-        <v>114</v>
-      </c>
-      <c r="D159" t="s">
-        <v>148</v>
-      </c>
-      <c r="E159" t="s">
-        <v>9</v>
-      </c>
-      <c r="F159" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>19330051920180</v>
-      </c>
-      <c r="B160" t="s">
-        <v>91</v>
-      </c>
-      <c r="C160" t="s">
-        <v>114</v>
-      </c>
-      <c r="D160" t="s">
-        <v>148</v>
-      </c>
-      <c r="E160" t="s">
-        <v>8</v>
-      </c>
-      <c r="F160" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>19330051920180</v>
-      </c>
-      <c r="B161" t="s">
-        <v>91</v>
-      </c>
-      <c r="C161" t="s">
-        <v>114</v>
-      </c>
-      <c r="D161" t="s">
-        <v>148</v>
-      </c>
-      <c r="E161" t="s">
-        <v>6</v>
-      </c>
-      <c r="F161" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>19330051920303</v>
-      </c>
-      <c r="B162" t="s">
-        <v>91</v>
-      </c>
-      <c r="C162" t="s">
-        <v>115</v>
-      </c>
-      <c r="D162" t="s">
-        <v>149</v>
-      </c>
-      <c r="E162" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163">
-        <v>19330051920303</v>
-      </c>
-      <c r="B163" t="s">
-        <v>91</v>
-      </c>
-      <c r="C163" t="s">
-        <v>115</v>
-      </c>
-      <c r="D163" t="s">
-        <v>149</v>
-      </c>
-      <c r="E163" t="s">
-        <v>7</v>
-      </c>
-      <c r="F163" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164">
-        <v>19330051920303</v>
-      </c>
-      <c r="B164" t="s">
-        <v>91</v>
-      </c>
-      <c r="C164" t="s">
-        <v>115</v>
-      </c>
-      <c r="D164" t="s">
-        <v>149</v>
-      </c>
-      <c r="E164" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165">
-        <v>19330051920303</v>
-      </c>
-      <c r="B165" t="s">
-        <v>91</v>
-      </c>
-      <c r="C165" t="s">
-        <v>115</v>
-      </c>
-      <c r="D165" t="s">
-        <v>149</v>
-      </c>
-      <c r="E165" t="s">
-        <v>8</v>
-      </c>
-      <c r="F165" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166">
-        <v>19330051920303</v>
-      </c>
-      <c r="B166" t="s">
-        <v>91</v>
-      </c>
-      <c r="C166" t="s">
-        <v>115</v>
-      </c>
-      <c r="D166" t="s">
-        <v>149</v>
-      </c>
-      <c r="E166" t="s">
-        <v>6</v>
-      </c>
-      <c r="F166" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167">
-        <v>19330051920182</v>
-      </c>
-      <c r="B167" t="s">
-        <v>92</v>
-      </c>
-      <c r="C167" t="s">
-        <v>116</v>
-      </c>
-      <c r="D167" t="s">
-        <v>150</v>
-      </c>
-      <c r="E167" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168">
-        <v>19330051920182</v>
-      </c>
-      <c r="B168" t="s">
-        <v>92</v>
-      </c>
-      <c r="C168" t="s">
-        <v>116</v>
-      </c>
-      <c r="D168" t="s">
-        <v>150</v>
-      </c>
-      <c r="E168" t="s">
-        <v>7</v>
-      </c>
-      <c r="F168" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169">
-        <v>19330051920182</v>
-      </c>
-      <c r="B169" t="s">
-        <v>92</v>
-      </c>
-      <c r="C169" t="s">
-        <v>116</v>
-      </c>
-      <c r="D169" t="s">
-        <v>150</v>
-      </c>
-      <c r="E169" t="s">
-        <v>9</v>
-      </c>
-      <c r="F169" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170">
-        <v>19330051920182</v>
-      </c>
-      <c r="B170" t="s">
-        <v>92</v>
-      </c>
-      <c r="C170" t="s">
-        <v>116</v>
-      </c>
-      <c r="D170" t="s">
-        <v>150</v>
-      </c>
-      <c r="E170" t="s">
-        <v>8</v>
-      </c>
-      <c r="F170" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171">
-        <v>19330051920182</v>
-      </c>
-      <c r="B171" t="s">
-        <v>92</v>
-      </c>
-      <c r="C171" t="s">
-        <v>116</v>
-      </c>
-      <c r="D171" t="s">
-        <v>150</v>
-      </c>
-      <c r="E171" t="s">
-        <v>6</v>
-      </c>
-      <c r="F171" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172">
-        <v>19330051920183</v>
-      </c>
-      <c r="B172" t="s">
-        <v>93</v>
-      </c>
-      <c r="C172" t="s">
-        <v>117</v>
-      </c>
-      <c r="D172" t="s">
-        <v>151</v>
-      </c>
-      <c r="E172" t="s">
-        <v>10</v>
-      </c>
-      <c r="F172" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173">
-        <v>19330051920183</v>
-      </c>
-      <c r="B173" t="s">
-        <v>93</v>
-      </c>
-      <c r="C173" t="s">
-        <v>117</v>
-      </c>
-      <c r="D173" t="s">
-        <v>151</v>
-      </c>
-      <c r="E173" t="s">
-        <v>7</v>
-      </c>
-      <c r="F173" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174">
-        <v>19330051920183</v>
-      </c>
-      <c r="B174" t="s">
-        <v>93</v>
-      </c>
-      <c r="C174" t="s">
-        <v>117</v>
-      </c>
-      <c r="D174" t="s">
-        <v>151</v>
-      </c>
-      <c r="E174" t="s">
-        <v>9</v>
-      </c>
-      <c r="F174" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175">
-        <v>19330051920183</v>
-      </c>
-      <c r="B175" t="s">
-        <v>93</v>
-      </c>
-      <c r="C175" t="s">
-        <v>117</v>
-      </c>
-      <c r="D175" t="s">
-        <v>151</v>
-      </c>
-      <c r="E175" t="s">
-        <v>8</v>
-      </c>
-      <c r="F175" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176">
-        <v>19330051920183</v>
-      </c>
-      <c r="B176" t="s">
-        <v>93</v>
-      </c>
-      <c r="C176" t="s">
-        <v>117</v>
-      </c>
-      <c r="D176" t="s">
-        <v>151</v>
-      </c>
-      <c r="E176" t="s">
-        <v>6</v>
-      </c>
-      <c r="F176" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7444,563 +4916,563 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920148</v>
+        <v>19330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920149</v>
+        <v>19330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920150</v>
+        <v>19330051920154</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920153</v>
+        <v>19330051920276</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920152</v>
+        <v>19330051920158</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920154</v>
+        <v>19330051920159</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920276</v>
+        <v>19330051920161</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920151</v>
+        <v>19330051920162</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920157</v>
+        <v>19330051920168</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920160</v>
+        <v>19330051920178</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920158</v>
+        <v>19330051920303</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920159</v>
+        <v>19330051920148</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920423</v>
+        <v>19330051920149</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920281</v>
+        <v>19330051920153</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920161</v>
+        <v>19330051920152</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920162</v>
+        <v>19330051920151</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920155</v>
+        <v>19330051920160</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920163</v>
+        <v>19330051920423</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920156</v>
+        <v>19330051920281</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920165</v>
+        <v>19330051920155</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920166</v>
+        <v>19330051920163</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920168</v>
+        <v>19330051920156</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920170</v>
+        <v>19330051920165</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920172</v>
+        <v>19330051920166</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920173</v>
+        <v>19330051920170</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920176</v>
+        <v>19330051920172</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920174</v>
+        <v>19330051920173</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920175</v>
+        <v>19330051920176</v>
       </c>
       <c r="B29" t="s">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920178</v>
+        <v>19330051920174</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920179</v>
+        <v>19330051920175</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920181</v>
+        <v>19330051920179</v>
       </c>
       <c r="B32" t="s">
         <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920180</v>
+        <v>19330051920181</v>
       </c>
       <c r="B33" t="s">
         <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920303</v>
+        <v>19330051920180</v>
       </c>
       <c r="B34" t="s">
         <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8017,7 +5489,7 @@
         <v>150</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8034,7 +5506,7 @@
         <v>151</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8044,7 +5516,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8074,6 +5546,903 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920150</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920150</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920154</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920154</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920158</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920158</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920159</v>
+      </c>
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920159</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920162</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920162</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920155</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920155</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920178</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920178</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920181</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920181</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920183</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920183</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920148</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920153</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920152</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>19330051920151</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>19330051920160</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>19330051920423</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>19330051920281</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>19330051920163</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>19330051920156</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>19330051920165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>19330051920166</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>19330051920170</v>
+      </c>
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>19330051920172</v>
+      </c>
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>19330051920173</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>19330051920174</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>19330051920175</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>19330051920179</v>
+      </c>
+      <c r="B38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>56</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>19330051920180</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>19330051920182</v>
+      </c>
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6ALCM - Estadisticos 20212.xlsx
+++ b/grupos/6ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="152">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Flores González Ángel</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Flores González Ángel</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -218,6 +218,81 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>COUDER</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MIXCOAC</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ONOFRE</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>YULIANA</t>
+  </si>
+  <si>
+    <t>ADRIANA ISABEL</t>
+  </si>
+  <si>
+    <t>MARIANA JOSELIN</t>
+  </si>
+  <si>
+    <t>JESE YAEL</t>
+  </si>
+  <si>
+    <t>ELYDEN JULYSSA</t>
+  </si>
+  <si>
+    <t>KATHERINE AZUL</t>
+  </si>
+  <si>
+    <t>ABRIL CITLALLI</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>MARLENE</t>
+  </si>
+  <si>
     <t>AYOCTLE</t>
   </si>
   <si>
@@ -236,33 +311,18 @@
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>COUDER</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -275,33 +335,18 @@
     <t>MARQUEZ</t>
   </si>
   <si>
-    <t>MIXCOAC</t>
-  </si>
-  <si>
     <t>MORENO</t>
   </si>
   <si>
     <t>OLTEHUA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>TEHUINTLE</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
@@ -320,9 +365,6 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>ESTRADA</t>
   </si>
   <si>
@@ -332,9 +374,6 @@
     <t>CARRERA</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
@@ -347,12 +386,6 @@
     <t>SEGURA</t>
   </si>
   <si>
-    <t>ONOFRE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -362,18 +395,12 @@
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>CARTEÑO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>KARLA</t>
   </si>
   <si>
@@ -392,15 +419,9 @@
     <t>MICHELL</t>
   </si>
   <si>
-    <t>YULIANA</t>
-  </si>
-  <si>
     <t>AYELEN</t>
   </si>
   <si>
-    <t>ADRIANA ISABEL</t>
-  </si>
-  <si>
     <t>KARIME GUADALUPE</t>
   </si>
   <si>
@@ -413,12 +434,6 @@
     <t>JUAN CARLOS</t>
   </si>
   <si>
-    <t>MARIANA JOSELIN</t>
-  </si>
-  <si>
-    <t>JESE YAEL</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
@@ -434,21 +449,12 @@
     <t>MARTHA</t>
   </si>
   <si>
-    <t>ELYDEN JULYSSA</t>
-  </si>
-  <si>
     <t>DIEGO MIGUEL</t>
   </si>
   <si>
     <t>JAXIRY JAZMIN</t>
   </si>
   <si>
-    <t>KATHERINE AZUL</t>
-  </si>
-  <si>
-    <t>ABRIL CITLALLI</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
@@ -464,16 +470,10 @@
     <t>KAROL</t>
   </si>
   <si>
-    <t>RUTH</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>MARLENE</t>
   </si>
 </sst>
 </file>
@@ -965,7 +965,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -1019,7 +1019,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1042,7 +1042,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>8</v>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1119,10 +1119,10 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1173,10 +1173,10 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1196,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1250,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1273,7 +1273,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -1327,7 +1327,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1350,7 +1350,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1404,7 +1404,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1430,7 +1430,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1484,7 +1484,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1504,10 +1504,10 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1558,10 +1558,10 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1581,7 +1581,7 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -1635,7 +1635,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1658,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1712,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1738,7 +1738,7 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -1792,7 +1792,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1812,10 +1812,10 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1866,10 +1866,10 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1889,7 +1889,7 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -1943,7 +1943,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1966,10 +1966,10 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -2020,10 +2020,10 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2043,7 +2043,7 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -2097,7 +2097,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2197,7 +2197,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -2251,7 +2251,7 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2274,10 +2274,10 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2328,10 +2328,10 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2351,7 +2351,7 @@
         <v>9</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>8</v>
@@ -2405,7 +2405,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2428,7 +2428,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2482,7 +2482,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2505,7 +2505,7 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -2559,7 +2559,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2585,7 +2585,7 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2659,7 +2659,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2736,7 +2736,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -2790,7 +2790,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2967,7 +2967,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3044,7 +3044,7 @@
         <v>8</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -3098,7 +3098,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3121,10 +3121,10 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3175,10 +3175,10 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3198,7 +3198,7 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E33">
         <v>8</v>
@@ -3252,7 +3252,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3275,7 +3275,7 @@
         <v>8</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -3329,7 +3329,7 @@
         <v>8</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3429,10 +3429,10 @@
         <v>9</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3483,10 +3483,10 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3506,7 +3506,7 @@
         <v>10</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E37">
         <v>8</v>
@@ -3560,7 +3560,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3711,27 +3711,30 @@
         <v>35</v>
       </c>
       <c r="D2">
+        <v>27</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>77.14</v>
+      </c>
+      <c r="G2">
+        <v>22.86</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>35</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3740,30 +3743,30 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>71.43000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>28.57</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3772,30 +3775,30 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>77.14</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G4">
-        <v>22.86</v>
+        <v>8.57</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3804,30 +3807,30 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G5">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2.86</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -3836,25 +3839,25 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>97.14</v>
+      </c>
+      <c r="G6">
+        <v>2.86</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>94.29000000000001</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.5</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5.71</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3896,7 +3899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3925,159 +3928,159 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920148</v>
+        <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920149</v>
+        <v>19330051920157</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920150</v>
+        <v>19330051920157</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920150</v>
+        <v>19330051920157</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920153</v>
+        <v>19330051920281</v>
       </c>
       <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
         <v>69</v>
       </c>
-      <c r="C6" t="s">
-        <v>97</v>
-      </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920152</v>
+        <v>19330051920161</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920154</v>
+        <v>19330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920154</v>
+        <v>19330051920173</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
@@ -4085,39 +4088,39 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920276</v>
+        <v>19330051920176</v>
       </c>
       <c r="B10" t="s">
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920276</v>
+        <v>19330051920180</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
         <v>89</v>
       </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
@@ -4125,762 +4128,22 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920151</v>
+        <v>19330051920183</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920157</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920157</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920157</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920157</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920160</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920158</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920158</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920159</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920159</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920423</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920281</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920161</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920161</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920162</v>
-      </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920162</v>
-      </c>
-      <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920155</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920163</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920156</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920165</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920166</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920168</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920168</v>
-      </c>
-      <c r="B34" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920170</v>
-      </c>
-      <c r="B35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920172</v>
-      </c>
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920173</v>
-      </c>
-      <c r="B37" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" t="s">
-        <v>141</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920176</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>142</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920174</v>
-      </c>
-      <c r="B39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" t="s">
-        <v>143</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920175</v>
-      </c>
-      <c r="B40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920178</v>
-      </c>
-      <c r="B41" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920178</v>
-      </c>
-      <c r="B42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920179</v>
-      </c>
-      <c r="B43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" t="s">
-        <v>75</v>
-      </c>
-      <c r="D43" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920181</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>147</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920180</v>
-      </c>
-      <c r="B45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920303</v>
-      </c>
-      <c r="B46" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" t="s">
-        <v>149</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920303</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920182</v>
-      </c>
-      <c r="B48" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920183</v>
-      </c>
-      <c r="B49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" t="s">
-        <v>117</v>
-      </c>
-      <c r="D49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4919,254 +4182,254 @@
         <v>19330051920157</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920150</v>
+        <v>19330051920276</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920154</v>
+        <v>19330051920281</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920276</v>
+        <v>19330051920161</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920158</v>
+        <v>19330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920159</v>
+        <v>19330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920161</v>
+        <v>19330051920176</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920162</v>
+        <v>19330051920180</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920168</v>
+        <v>19330051920183</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920178</v>
+        <v>19330051920148</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920303</v>
+        <v>19330051920149</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920148</v>
+        <v>19330051920150</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920149</v>
+        <v>19330051920153</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920153</v>
+        <v>19330051920152</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920152</v>
+        <v>19330051920154</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5174,16 +4437,16 @@
         <v>19330051920151</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5191,203 +4454,203 @@
         <v>19330051920160</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920423</v>
+        <v>19330051920158</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920281</v>
+        <v>19330051920159</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920155</v>
+        <v>19330051920423</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920163</v>
+        <v>19330051920162</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920156</v>
+        <v>19330051920155</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920165</v>
+        <v>19330051920163</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920166</v>
+        <v>19330051920156</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920170</v>
+        <v>19330051920165</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920172</v>
+        <v>19330051920166</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920173</v>
+        <v>19330051920170</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920176</v>
+        <v>19330051920172</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5395,16 +4658,16 @@
         <v>19330051920174</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5412,101 +4675,101 @@
         <v>19330051920175</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920179</v>
+        <v>19330051920178</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920181</v>
+        <v>19330051920179</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920180</v>
+        <v>19330051920181</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920182</v>
+        <v>19330051920303</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
         <v>150</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920183</v>
+        <v>19330051920182</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>151</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5516,7 +4779,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5548,91 +4811,91 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920149</v>
+        <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920149</v>
+        <v>19330051920276</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920150</v>
+        <v>19330051920161</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920150</v>
+        <v>19330051920161</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5640,22 +4903,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920154</v>
+        <v>19330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5663,45 +4926,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920154</v>
+        <v>19330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920158</v>
+        <v>19330051920183</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5709,65 +4972,65 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920158</v>
+        <v>19330051920183</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920159</v>
+        <v>19330051920149</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920159</v>
+        <v>19330051920281</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
@@ -5778,42 +5041,42 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920162</v>
+        <v>19330051920155</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920162</v>
+        <v>19330051920173</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>57</v>
@@ -5824,623 +5087,71 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920155</v>
+        <v>19330051920181</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920155</v>
+        <v>19330051920180</v>
       </c>
       <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
         <v>80</v>
       </c>
-      <c r="C15" t="s">
-        <v>106</v>
-      </c>
       <c r="D15" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920178</v>
+        <v>19330051920303</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>56</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920178</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920181</v>
-      </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920181</v>
-      </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
         <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920183</v>
-      </c>
-      <c r="B20" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920183</v>
-      </c>
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920148</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920153</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920152</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920151</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920160</v>
-      </c>
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920423</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D27" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920281</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>19330051920163</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920156</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920165</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>19330051920166</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>19330051920170</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>19330051920172</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>19330051920173</v>
-      </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>19330051920174</v>
-      </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>19330051920175</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>19330051920179</v>
-      </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" t="s">
-        <v>146</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>19330051920180</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" t="s">
-        <v>148</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>56</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>19330051920182</v>
-      </c>
-      <c r="B40" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" t="s">
-        <v>150</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ALCM - Estadisticos 20212.xlsx
+++ b/grupos/6ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -86,9 +86,6 @@
     <t>DE LA LUZ SANCHEZ JUAN MANUEL</t>
   </si>
   <si>
-    <t>ELIZALDE JUAREZ ADRIANA ISABEL</t>
-  </si>
-  <si>
     <t>GAMEZ SILVERIO MICAELA</t>
   </si>
   <si>
@@ -188,18 +185,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
+    <t>Flores González Ángel</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Flores González Ángel</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>COUDER</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -245,9 +239,6 @@
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>TETLA</t>
   </si>
   <si>
@@ -267,9 +258,6 @@
   </si>
   <si>
     <t>YULIANA</t>
-  </si>
-  <si>
-    <t>ADRIANA ISABEL</t>
   </si>
   <si>
     <t>MARIANA JOSELIN</t>
@@ -831,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -977,16 +965,16 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1022,7 +1010,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1051,19 +1039,19 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1093,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1105,7 +1093,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1131,16 +1119,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1170,13 +1158,13 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1208,16 +1196,16 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1244,16 +1232,16 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1285,16 +1273,16 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1330,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1362,16 +1350,16 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1407,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1439,10 +1427,10 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1475,7 +1463,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1516,16 +1504,16 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1561,7 +1549,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1593,10 +1581,10 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1629,10 +1617,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1670,16 +1658,16 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1715,7 +1703,7 @@
         <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1729,34 +1717,34 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1783,22 +1771,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1815,7 +1803,7 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1824,16 +1812,16 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1883,34 +1871,34 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1937,22 +1925,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1960,34 +1948,34 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2014,19 +2002,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2037,34 +2025,34 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2091,22 +2079,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2114,34 +2102,34 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2168,22 +2156,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2194,31 +2182,31 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2248,19 +2236,19 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2268,34 +2256,34 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>9</v>
       </c>
       <c r="D21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2322,19 +2310,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2348,31 +2336,31 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2405,16 +2393,16 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>8</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2422,34 +2410,34 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23">
         <v>10</v>
       </c>
       <c r="G23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2476,22 +2464,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2499,34 +2487,34 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>8</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="E24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24">
         <v>10</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2553,13 +2541,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2568,7 +2556,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2576,34 +2564,34 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25">
         <v>10</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2630,22 +2618,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2659,28 +2647,28 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>10</v>
       </c>
       <c r="G26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2713,7 +2701,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2722,7 +2710,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2736,28 +2724,28 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>10</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2790,16 +2778,16 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2810,31 +2798,31 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>-1</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2864,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -2873,10 +2861,10 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2887,31 +2875,31 @@
         <v>10</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29">
         <v>9</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2941,19 +2929,19 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2964,31 +2952,31 @@
         <v>10</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30">
         <v>8</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -3021,16 +3009,16 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3041,13 +3029,13 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -3056,16 +3044,16 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3095,13 +3083,13 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3121,28 +3109,28 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32">
         <v>10</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3175,16 +3163,16 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3192,28 +3180,28 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>9</v>
       </c>
       <c r="E33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>10</v>
       </c>
       <c r="G33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3246,22 +3234,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>9</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3269,34 +3257,34 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34">
         <v>10</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3323,22 +3311,22 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3346,28 +3334,28 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>10</v>
       </c>
       <c r="G35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3400,22 +3388,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3423,34 +3411,34 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36">
         <v>10</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3477,22 +3465,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3500,28 +3488,28 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="E37">
         <v>8</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3554,98 +3542,21 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="W37">
         <v>8</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y37">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-      <c r="C38">
-        <v>8</v>
-      </c>
-      <c r="D38">
-        <v>-1</v>
-      </c>
-      <c r="E38">
-        <v>8</v>
-      </c>
-      <c r="F38">
-        <v>8</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-      <c r="H38">
-        <v>-1</v>
-      </c>
-      <c r="I38">
-        <v>-1</v>
-      </c>
-      <c r="J38">
-        <v>-1</v>
-      </c>
-      <c r="K38">
-        <v>-1</v>
-      </c>
-      <c r="L38">
-        <v>-1</v>
-      </c>
-      <c r="M38">
-        <v>-1</v>
-      </c>
-      <c r="N38">
-        <v>-1</v>
-      </c>
-      <c r="O38">
-        <v>-1</v>
-      </c>
-      <c r="P38">
-        <v>-1</v>
-      </c>
-      <c r="Q38">
-        <v>-1</v>
-      </c>
-      <c r="R38">
-        <v>-1</v>
-      </c>
-      <c r="S38">
-        <v>-1</v>
-      </c>
-      <c r="T38">
-        <v>8</v>
-      </c>
-      <c r="U38">
-        <v>8</v>
-      </c>
-      <c r="V38">
-        <v>-1</v>
-      </c>
-      <c r="W38">
-        <v>8</v>
-      </c>
-      <c r="X38">
-        <v>8</v>
-      </c>
-      <c r="Y38">
         <v>5</v>
       </c>
     </row>
@@ -3673,159 +3584,159 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>27</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="G2">
-        <v>22.86</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="G3">
+        <v>17.65</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>77.14</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>22.86</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>88.56999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="G4">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>33</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>97.06</v>
+      </c>
+      <c r="G5">
+        <v>2.94</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>94.29000000000001</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>9.5</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5.71</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3833,25 +3744,25 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>34</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3865,13 +3776,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3883,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3899,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3908,16 +3819,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -3931,219 +3842,159 @@
         <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920157</v>
+        <v>19330051920281</v>
       </c>
       <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
         <v>67</v>
       </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920157</v>
+        <v>19330051920161</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920157</v>
+        <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920281</v>
+        <v>19330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920161</v>
+        <v>19330051920176</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
         <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920168</v>
+        <v>19330051920180</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
         <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920173</v>
+        <v>19330051920183</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
         <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920176</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920180</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4153,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4162,50 +4013,50 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920157</v>
+        <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920276</v>
+        <v>19330051920281</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4213,16 +4064,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920281</v>
+        <v>19330051920161</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4230,16 +4081,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920161</v>
+        <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -4247,16 +4098,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920168</v>
+        <v>19330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -4264,16 +4115,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920173</v>
+        <v>19330051920176</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4281,16 +4132,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920176</v>
+        <v>19330051920180</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4298,16 +4149,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920180</v>
+        <v>19330051920183</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4315,33 +4166,33 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920183</v>
+        <v>19330051920148</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920148</v>
+        <v>19330051920149</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4349,16 +4200,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920149</v>
+        <v>19330051920150</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4366,16 +4217,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920150</v>
+        <v>19330051920153</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4383,16 +4234,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920153</v>
+        <v>19330051920152</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4400,16 +4251,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920152</v>
+        <v>19330051920154</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4417,16 +4268,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920154</v>
+        <v>19330051920151</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4434,16 +4285,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920151</v>
+        <v>19330051920160</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4451,16 +4302,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920160</v>
+        <v>19330051920158</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4468,16 +4319,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920158</v>
+        <v>19330051920159</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4485,16 +4336,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920159</v>
+        <v>19330051920423</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4502,16 +4353,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920423</v>
+        <v>19330051920162</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4519,16 +4370,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920162</v>
+        <v>19330051920155</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4536,16 +4387,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920155</v>
+        <v>19330051920163</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4553,16 +4404,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920163</v>
+        <v>19330051920156</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4570,16 +4421,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920156</v>
+        <v>19330051920165</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4587,16 +4438,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920165</v>
+        <v>19330051920166</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4604,16 +4455,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920166</v>
+        <v>19330051920170</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4621,16 +4472,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920170</v>
+        <v>19330051920172</v>
       </c>
       <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4638,16 +4489,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920172</v>
+        <v>19330051920174</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4655,16 +4506,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920174</v>
+        <v>19330051920175</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4672,16 +4523,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920175</v>
+        <v>19330051920178</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4689,16 +4540,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920178</v>
+        <v>19330051920179</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4706,16 +4557,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920179</v>
+        <v>19330051920181</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -4723,16 +4574,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920181</v>
+        <v>19330051920303</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4740,35 +4591,18 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920303</v>
+        <v>19330051920182</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>19330051920182</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36">
         <v>0</v>
       </c>
     </row>
@@ -4788,22 +4622,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4814,13 +4648,13 @@
         <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4837,19 +4671,19 @@
         <v>19330051920276</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4857,68 +4691,68 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920161</v>
+        <v>19330051920168</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920161</v>
+        <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920168</v>
+        <v>19330051920176</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -4926,16 +4760,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920168</v>
+        <v>19330051920176</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4952,19 +4786,19 @@
         <v>19330051920183</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -4975,13 +4809,13 @@
         <v>19330051920183</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4995,42 +4829,42 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920149</v>
+        <v>19330051920281</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920281</v>
+        <v>19330051920161</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
@@ -5044,13 +4878,13 @@
         <v>19330051920155</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -5067,19 +4901,19 @@
         <v>19330051920173</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -5090,13 +4924,13 @@
         <v>19330051920181</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5113,19 +4947,19 @@
         <v>19330051920180</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -5136,13 +4970,13 @@
         <v>19330051920303</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>

--- a/grupos/6ALCM - Estadisticos 20212.xlsx
+++ b/grupos/6ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
+    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -215,34 +215,127 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AYOCTLE</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>COUDER</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>MIXCOAC</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>BERUDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
   </si>
   <si>
     <t>ONOFRE</t>
@@ -251,217 +344,124 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CARTEÑO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IAN ISSAID</t>
+  </si>
+  <si>
+    <t>EMMA NOHEMI</t>
+  </si>
+  <si>
+    <t>MAYTE DOLORES</t>
+  </si>
+  <si>
+    <t>MICHELL</t>
+  </si>
+  <si>
     <t>YULIANA</t>
   </si>
   <si>
+    <t>AYELEN</t>
+  </si>
+  <si>
+    <t>KARIME GUADALUPE</t>
+  </si>
+  <si>
+    <t>MICAELA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
     <t>MARIANA JOSELIN</t>
   </si>
   <si>
     <t>JESE YAEL</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>MARTHA</t>
+  </si>
+  <si>
     <t>ELYDEN JULYSSA</t>
   </si>
   <si>
+    <t>DIEGO MIGUEL</t>
+  </si>
+  <si>
+    <t>JAXIRY JAZMIN</t>
+  </si>
+  <si>
     <t>KATHERINE AZUL</t>
   </si>
   <si>
     <t>ABRIL CITLALLI</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>LIZETH</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>DANNA ARLETTE</t>
+  </si>
+  <si>
+    <t>KAROL</t>
+  </si>
+  <si>
     <t>RUTH</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
     <t>MARLENE</t>
-  </si>
-  <si>
-    <t>AYOCTLE</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>BERUDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CARTEÑO</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IAN ISSAID</t>
-  </si>
-  <si>
-    <t>EMMA NOHEMI</t>
-  </si>
-  <si>
-    <t>MAYTE DOLORES</t>
-  </si>
-  <si>
-    <t>MICHELL</t>
-  </si>
-  <si>
-    <t>AYELEN</t>
-  </si>
-  <si>
-    <t>KARIME GUADALUPE</t>
-  </si>
-  <si>
-    <t>MICAELA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO EMMANUEL</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>MARTHA</t>
-  </si>
-  <si>
-    <t>DIEGO MIGUEL</t>
-  </si>
-  <si>
-    <t>JAXIRY JAZMIN</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>LIZETH</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>DANNA ARLETTE</t>
-  </si>
-  <si>
-    <t>KAROL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
   </si>
 </sst>
 </file>
@@ -971,16 +971,16 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1016,7 +1016,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1048,16 +1048,16 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1125,16 +1125,16 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1167,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1202,16 +1202,16 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1247,7 +1247,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1279,16 +1279,16 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1315,16 +1315,16 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1356,16 +1356,16 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1415,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1433,16 +1433,16 @@
         <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1469,16 +1469,16 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1510,16 +1510,16 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1546,7 +1546,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1587,16 +1587,16 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1623,10 +1623,10 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1664,16 +1664,16 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1706,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1741,16 +1741,16 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1818,16 +1818,16 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1895,16 +1895,16 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1931,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1972,16 +1972,16 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2008,7 +2008,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2017,7 +2017,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2031,7 +2031,7 @@
         <v>8</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2049,16 +2049,16 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2085,16 +2085,16 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2114,7 +2114,7 @@
         <v>8</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -2126,16 +2126,16 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2162,13 +2162,13 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2203,16 +2203,16 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2245,10 +2245,10 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2280,16 +2280,16 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2316,13 +2316,13 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2357,16 +2357,16 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2393,7 +2393,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2402,7 +2402,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2434,16 +2434,16 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2479,7 +2479,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2493,7 +2493,7 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2517,10 +2517,10 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2547,13 +2547,13 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2588,16 +2588,16 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2665,16 +2665,16 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2724,7 +2724,7 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -2742,16 +2742,16 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2778,7 +2778,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2787,7 +2787,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2801,7 +2801,7 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2819,16 +2819,16 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2855,7 +2855,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2864,7 +2864,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2896,16 +2896,16 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2941,7 +2941,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2973,16 +2973,16 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3050,16 +3050,16 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3127,16 +3127,16 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3172,7 +3172,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3207,13 +3207,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3243,13 +3243,13 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3263,7 +3263,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>8</v>
@@ -3281,16 +3281,16 @@
         <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3326,7 +3326,7 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3361,13 +3361,13 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3397,13 +3397,13 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3435,16 +3435,16 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3494,7 +3494,7 @@
         <v>8</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>8</v>
@@ -3512,16 +3512,16 @@
         <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3548,16 +3548,16 @@
         <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3622,30 +3622,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3654,19 +3654,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G3">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3689,27 +3689,27 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>97.06</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3718,19 +3718,19 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3810,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3835,166 +3835,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920276</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920281</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920161</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920173</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920176</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920180</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920183</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4030,149 +3870,149 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920276</v>
+        <v>19330051920148</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920281</v>
+        <v>19330051920149</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920161</v>
+        <v>19330051920150</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920168</v>
+        <v>19330051920153</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920173</v>
+        <v>19330051920152</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920176</v>
+        <v>19330051920154</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920180</v>
+        <v>19330051920276</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920183</v>
+        <v>19330051920151</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920148</v>
+        <v>19330051920160</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>123</v>
@@ -4183,13 +4023,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920149</v>
+        <v>19330051920158</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
         <v>124</v>
@@ -4200,13 +4040,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920150</v>
+        <v>19330051920159</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -4217,13 +4057,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920153</v>
+        <v>19330051920423</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>126</v>
@@ -4234,13 +4074,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920152</v>
+        <v>19330051920281</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>127</v>
@@ -4251,13 +4091,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920154</v>
+        <v>19330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
         <v>128</v>
@@ -4268,13 +4108,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920151</v>
+        <v>19330051920162</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>129</v>
@@ -4285,13 +4125,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920160</v>
+        <v>19330051920155</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>130</v>
@@ -4302,13 +4142,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920158</v>
+        <v>19330051920163</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
         <v>131</v>
@@ -4319,13 +4159,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920159</v>
+        <v>19330051920156</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>132</v>
@@ -4336,13 +4176,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920423</v>
+        <v>19330051920165</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4353,16 +4193,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920162</v>
+        <v>19330051920166</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4370,16 +4210,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920155</v>
+        <v>19330051920168</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4387,16 +4227,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920163</v>
+        <v>19330051920170</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4404,16 +4244,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920156</v>
+        <v>19330051920172</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4421,16 +4261,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920165</v>
+        <v>19330051920173</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4438,16 +4278,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920166</v>
+        <v>19330051920176</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4455,13 +4295,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920170</v>
+        <v>19330051920174</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4472,13 +4312,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920172</v>
+        <v>19330051920175</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4489,13 +4329,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920174</v>
+        <v>19330051920178</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4506,13 +4346,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920175</v>
+        <v>19330051920179</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4523,13 +4363,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920178</v>
+        <v>19330051920181</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4540,13 +4380,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920179</v>
+        <v>19330051920180</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4557,13 +4397,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920181</v>
+        <v>19330051920303</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4574,13 +4414,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920303</v>
+        <v>19330051920182</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -4591,13 +4431,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920182</v>
+        <v>19330051920183</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D35" t="s">
         <v>147</v>
@@ -4613,7 +4453,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4648,19 +4488,19 @@
         <v>19330051920276</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4671,22 +4511,22 @@
         <v>19330051920276</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4694,22 +4534,22 @@
         <v>19330051920168</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4717,19 +4557,19 @@
         <v>19330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4737,254 +4577,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920176</v>
+        <v>19330051920155</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
       </c>
       <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920176</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920183</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920183</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920281</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920161</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920155</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920173</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920181</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920180</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920303</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCM - Estadisticos 20212.xlsx
+++ b/grupos/6ALCM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -185,19 +185,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
+    <t>Flores González Ángel</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Flores González Ángel</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
@@ -983,22 +983,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1060,22 +1060,22 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1087,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1137,22 +1137,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1161,10 +1161,10 @@
         <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1214,22 +1214,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1238,13 +1238,13 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1291,22 +1291,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1368,22 +1368,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1445,34 +1445,34 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1522,22 +1522,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1546,10 +1546,10 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1599,40 +1599,40 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
+        <v>7</v>
+      </c>
+      <c r="X12">
+        <v>9</v>
+      </c>
+      <c r="Y12">
         <v>6</v>
-      </c>
-      <c r="X12">
-        <v>10</v>
-      </c>
-      <c r="Y12">
-        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1676,22 +1676,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1753,22 +1753,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1830,22 +1830,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1898,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>8</v>
@@ -1907,22 +1907,22 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1934,7 +1934,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1984,22 +1984,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2061,28 +2061,28 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2091,7 +2091,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2138,22 +2138,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2215,22 +2215,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2292,22 +2292,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2316,7 +2316,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2369,28 +2369,28 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2446,22 +2446,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2511,7 +2511,7 @@
         <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -2523,28 +2523,28 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>7</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2600,22 +2600,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2677,22 +2677,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2754,22 +2754,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2778,7 +2778,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2831,25 +2831,25 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2908,22 +2908,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2985,22 +2985,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3062,22 +3062,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3139,22 +3139,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>5</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>8</v>
@@ -3216,22 +3216,22 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3240,13 +3240,13 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3293,28 +3293,28 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3358,7 +3358,7 @@
         <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>9</v>
@@ -3370,22 +3370,22 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3394,10 +3394,10 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3447,22 +3447,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3524,22 +3524,22 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3557,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3622,19 +3622,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G2">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3654,19 +3654,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3686,19 +3686,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4453,7 +4453,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4485,116 +4485,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920276</v>
+        <v>19330051920168</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920276</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920168</v>
-      </c>
-      <c r="B4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920155</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>
